--- a/ground-truth/expert-validation/CCoP_V2_Test_Cases_Expert_Review.xlsx
+++ b/ground-truth/expert-validation/CCoP_V2_Test_Cases_Expert_Review.xlsx
@@ -645,12 +645,12 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Scope</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>Section 11 Cybersecurity Act, RESPONSE-TO-FEEDBACK Q2.2-2.3</t>
+          <t>1.2.1, 1.4.1 [support: Cybersecurity Act 2018 §7, RESPONSE-TO-FEEDBACK Q2.2-2.3]</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -1877,12 +1877,12 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Section 5: Protection</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 5.1.5, CCoP 2.0 Section 5.3</t>
+          <t>5.1.2, 5.3.1, 5.7.2</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>Section 5: Protection</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>5.1.5</t>
+          <t>5.1.2, 5.7.2</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>This configuration is compliant with CCoP 2.0 Clause 5.1.5. It implements two independent authentication factors: something you know (password) and something you have (mobile phone receiving SMS). CCoP 2.0 requires MFA but does not prohibit SMS-based codes or prescribe specific MFA technologies. The requirement is satisfied by combining two independent factors. While NIST recommends stronger MFA than SMS due to SIM swapping risks, and while banking sector best practices may favour app-based or hardware token MFA, the regulatory minimum set by CCoP 2.0 is met. An auditor would not reject this configuration solely based on the SMS factor type, provided the MFA is enforced for all remote access to the CII.</t>
+          <t>This configuration is compliant with CCoP 2.0 Clause 5.7.2(b). It implements two independent authentication factors: something you know (password) and something you have (mobile phone receiving SMS). CCoP 2.0 requires MFA but does not prohibit SMS-based codes or prescribe specific MFA technologies. The requirement is satisfied by combining two independent factors. While NIST recommends stronger MFA than SMS due to SIM swapping risks, and while banking sector best practices may favour app-based or hardware token MFA, the regulatory minimum set by CCoP 2.0 is met. An auditor would not reject this configuration solely based on the SMS factor type, provided the MFA is enforced for all remote access to the CII.</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>Section 5: Protection</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>5.6.4</t>
+          <t>5.10.1(e)</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>This configuration is compliant with CCoP 2.0 Clause 5.6.4. The clause requires critical patches — those addressing vulnerabilities with active exploitation or publicly available exploit code — to be applied within two weeks (14 days) of vendor release. Deploying on January 13, which is 13 days after January 1, falls within the 14-day compliance window. The testing period does not create a compliance issue — appropriate testing before deployment is expected and the timeline still meets the requirement. In the OT context, testing patches in an isolated lab before deploying to production SCADA is good practice. The compliance status is met regardless of the OT environment complexity.</t>
+          <t>This configuration is compliant with CCoP 2.0 Clause 5.10.1(e), which requires security patches to be applied in a timely manner to reduce cybersecurity vulnerabilities, and Clause 5.10.1(d), which requires prioritising patch application based on the level of risk posed to the operations of the CII. A prompt deployment (within roughly two weeks) of a critical patch addressing a vulnerability with active exploitation or publicly available exploit code — including a short testing phase — reflects appropriate risk-based prioritisation and timely application. Clause 5.10.1(c) expects patches to be tested in an environment similar to the CII production environment before deployment; the testing period described does not compromise compliance. In the OT context, testing patches in an isolated lab before deploying to production SCADA is good practice. CCoP 2.0 does not prescribe a fixed number of days — 'timely' is a risk-based determination — and the documented process meets that standard.</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Section 5: Protection</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>5.6.4</t>
+          <t>5.10.1(e)</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>This configuration is partially non-compliant. CCoP 2.0 Clause 5.6.4 requires: (1) critical patches — those addressing vulnerabilities with active exploitation or publicly available exploit code — applied within 14 days; and (2) other security patches applied within one month (approximately 30 days). The critical patch timeline of 14 days is compliant. However, the non-critical patch timeline of 25 days may or may not be compliant depending on interpretation: 25 days is within the one-month window if 'one month' is interpreted as 30-31 calendar days. A 25-day automated deployment for non-critical patches is within the one-month requirement and therefore compliant for the non-critical category. Both timelines comply. This configuration is fully compliant with CCoP 2.0 Clause 5.6.4.</t>
+          <t>This configuration is compliant with CCoP 2.0 Clause 5.10.1. Clause 5.10.1(e) requires security patches to be applied in a timely manner; Clause 5.10.1(d) requires prioritisation based on the level of risk posed to operations. Applying critical patches (active exploitation or public exploit code) within about two weeks and non-critical patches within about three to four weeks is consistent with the timely, risk-prioritised application the clause expects. CCoP 2.0 does not prescribe a fixed number of days — timeliness is a risk-based determination. The two-track automated deployment process described also aligns with Clause 5.10.1(a) monitoring of patch releases, 5.10.1(b) integrity verification, 5.10.1(c) testing prior to deployment, and 5.10.1(f) monitoring and tracking of patching progress.</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>Section 5: Protection</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>5.6.4, 5.6.2</t>
+          <t>5.10.1(e)</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>This is a partially compliant situation that likely requires a waiver. CCoP 2.0 Clause 5.6.4 requires patching within specified timelines, but when a vendor no longer supports equipment and issues no patches, there is no patch to apply. This creates a genuine technical infeasibility. The compensating controls — network isolation, enhanced monitoring, and annual manual security review — are appropriate responses to unpatched legacy OT equipment. However, operating end-of-life equipment with known unresolved vulnerabilities on CII is a compliance risk that the CIIO should address through the waiver process under Section 11(7). The waiver application should document: the genuine impossibility of patching, the compensating controls in place, a timeline for equipment replacement or upgrade, and ongoing monitoring commitments. The compensating controls alone do not achieve full compliance with Clause 5.6.4 — a waiver formalizes and legitimizes the compensating control approach.</t>
+          <t>This is a partially compliant situation that likely requires a waiver. CCoP 2.0 Clause 5.10.1 requires security patches to be applied in a timely manner with prioritisation based on risk. When a vendor no longer supports equipment and issues no patches, there is no patch to apply — creating a genuine technical infeasibility. Clause 5.10.1(g) expects compensating controls to mitigate and reduce cybersecurity risks in cases where a security patch cannot be applied: network isolation, enhanced monitoring, and annual manual security review are appropriate responses to unpatched legacy OT equipment. However, operating end-of-life equipment with known unresolved vulnerabilities on CII is a compliance risk that the CIIO should address through the waiver process (Clause 1.6), which aligns with Section 11(7) of the Cybersecurity Act. The waiver application should document the genuine impossibility of patching, the 5.10.1(g) compensating controls in place, a timeline for equipment replacement or upgrade, and ongoing monitoring commitments. Compensating controls alone do not achieve full compliance with Clause 5.10 — a waiver formalises and legitimises the compensating control approach.</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>Section 5: Protection</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>5.6.4</t>
+          <t>5.10.1(e)</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>This situation is non-compliant with CCoP 2.0 Clause 5.6.4 for the specific critical patch. Clause 5.6.4 requires critical patches — those addressing vulnerabilities with active exploitation or publicly available exploit code — to be applied within 14 days of vendor release. The 28-day application timeline, even when constrained by a quarterly maintenance window schedule, exceeds the 14-day requirement. The quarterly maintenance window schedule cannot override the 14-day critical patch obligation. For critical patches, the organization must either: (1) adjust the maintenance window schedule to allow emergency patching within 14 days for critical patches; (2) implement compensating controls (increased monitoring, network isolation) while pursuing emergency patching approval; or (3) if the patch genuinely cannot be applied within 14 days due to operational constraints, submit a waiver request. Quarterly patch cycles are acceptable for non-critical patches (one-month window) but not for critical patches.</t>
+          <t>This situation is non-compliant with CCoP 2.0 Clause 5.10.1(e) and Clause 5.10.1(d) for the specific critical patch. Clause 5.10.1(d) requires prioritising patch application based on the level of risk posed to operations; Clause 5.10.1(e) requires applying security patches in a timely manner to reduce cybersecurity vulnerabilities. Waiting for a fixed quarterly maintenance window before applying a critical patch for a vulnerability with active exploitation or a publicly available exploit does not reflect risk-based prioritisation or timeliness. A rigid quarterly maintenance schedule cannot override the Clause 5.10.1(d)/(e) obligation for critical patches. The organisation must either: (1) adjust the maintenance window schedule to allow out-of-cycle emergency patching for critical patches; (2) where that is genuinely infeasible, implement Clause 5.10.1(g) compensating controls (increased monitoring, network isolation) while pursuing emergency patching approval; or (3) if the patch cannot be applied in the near term, submit a waiver request under Clause 1.6, aligned with Section 11(7) of the Cybersecurity Act. Quarterly patch cycles may be acceptable for lower-risk non-critical patches when documented under Clause 5.10.1(d) risk-based prioritisation, but not for critical patches.</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>5.3.1(c)</t>
+          <t>5.2.1, 5.3.1(c)</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>5.4.1</t>
+          <t>5.5.1, 5.5.2, 10.2.1</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>A flat OT network with no segmentation does not comply with CCoP 2.0 requirements. Section 5.4.1 explicitly requires network segmentation to limit the blast radius of security incidents. Connecting PLCs directly to the corporate network without segmentation exposes critical control systems to threats originating in IT environments. Physical security of the control room does not address cyber threats. The reference to Section 10 (OT-specific requirements) reinforces that OT systems must be segmented from IT networks. A demilitarized zone (DMZ) or proper network segmentation must be implemented to isolate OT systems.</t>
+          <t>A flat OT network with no segmentation does not comply with CCoP 2.0 requirements. Section 5.5 explicitly requires network segmentation to limit the blast radius of security incidents. Connecting PLCs directly to the corporate network without segmentation exposes critical control systems to threats originating in IT environments. Physical security of the control room does not address cyber threats. The reference to Section 10 (OT-specific requirements) reinforces that OT systems must be segmented from IT networks. A demilitarized zone (DMZ) or proper network segmentation must be implemented to isolate OT systems.</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>5.2.1, 5.3.1(c)</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
-          <t>Temporary use of shared accounts does not comply. CCoP 5.3.1 requires individual accountability regardless of transition status. Use service accounts with proper credentials for each administrator or implement role-based access.</t>
+          <t>Temporary use of shared accounts does not comply. CCoP 5.2.1 / 5.3.1(c) requires individual accountability regardless of transition status. Use service accounts with proper credentials for each administrator or implement role-based access.</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>5.3.1,11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>5.3.2</t>
+          <t>5.1.4</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="K56" s="6" t="inlineStr">
         <is>
-          <t>8-hour session timeout exceeds reasonable session management. CCoP 5.3.2 requires appropriate session timeout commensurate with risk. ATC systems are high-consequence; extended sessions increase risk of unauthorized access if a workstation is left unattended. Implement 30-60 minute timeout with re-authentication.</t>
+          <t>8-hour session timeout exceeds reasonable session management. CCoP 5.1.4 requires appropriate session timeout commensurate with risk. ATC systems are high-consequence; extended sessions increase risk of unauthorized access if a workstation is left unattended. Implement 30-60 minute timeout with re-authentication.</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -4880,12 +4880,12 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>5.10.1, 5.10.2</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>Quarterly patching may be acceptable with a documented risk assessment and compensating controls. CCoP 4.2 requires systems be kept up to date but allows operational constraints. The organization must document: (1) monthly patching infeasibility, (2) compensating monitoring, (3) isolation from less critical systems.</t>
+          <t>Quarterly patching may be acceptable with a documented risk assessment and compensating controls. CCoP 5.10 requires systems be kept up to date but allows operational constraints. The organization must document: (1) monthly patching infeasibility, (2) compensating monitoring, (3) isolation from less critical systems.</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -4957,12 +4957,12 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>3.8.1, 3.8.3, 3.8.4</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
-          <t>Service providers to CII organizations have additional obligations under CCoP Section 7. You must establish contractual security requirements, conduct due diligence on the CII's security posture, and have security incident notification clauses. Standard commercial SLA does not meet CCoP requirements.</t>
+          <t>Service providers to CII organizations have additional obligations under CCoP Section 3.8. You must establish contractual security requirements, conduct due diligence on the CII's security posture, and have security incident notification clauses. Standard commercial SLA does not meet CCoP requirements.</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.7.1, 3.7.3</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>Cloud provider certifications do not eliminate the CII organization's security obligations. CCoP Section 5 applies regardless of hosting model. The agency must implement its own access controls, monitoring, and incident response. Cloud provider security is a shared responsibility model, not a complete delegation.</t>
+          <t>Cloud provider certifications do not eliminate the CII organization's security obligations. CCoP Section 3.7 applies regardless of hosting model. The agency must implement its own access controls, monitoring, and incident response. Cloud provider security is a shared responsibility model, not a complete delegation.</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>3.2.1, 3.2.5</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="K60" s="6" t="inlineStr">
         <is>
-          <t>CCoP Section 2 requires annual risk assessment and periodic compliance review. Technology and threat landscapes evolve. CCoP 2.0 was updated in 2024; previous compliance does not guarantee continued compliance. Annual reassessment is mandatory.</t>
+          <t>CCoP Section 3.2 requires annual risk assessment and periodic compliance review. Technology and threat landscapes evolve. CCoP 2.0 was updated in 2024; previous compliance does not guarantee continued compliance. Annual reassessment is mandatory.</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.8.1, 3.8.2, 3.8.3</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>Outsourced monitoring can satisfy Section 5.2 if internal visibility is maintained. The port must have real-time access to alerts, ability to direct investigation response, and clear SLAs. The MSSP acts as an extension of the CII's security function, not a complete replacement.</t>
+          <t>Outsourced monitoring can satisfy Section 3.8 if internal visibility is maintained. The port must have real-time access to alerts, ability to direct investigation response, and clear SLAs. The MSSP acts as an extension of the CII's security function, not a complete replacement.</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>3.1.1, 3.8.1</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>5.3.1(c)</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>5.3.1(a), 5.3.1(c)</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>3.1.1, 3.3.1</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
@@ -5650,12 +5650,12 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>3.8.1, 5.7.1, 5.7.2</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>Third-party remote access to CII systems requires enhanced monitoring per CCoP Section 7. ISO 27001 does not exempt the need for: (1) session logging for all remote access, (2) activity monitoring, (3) least privilege access, (4) periodic access review.</t>
+          <t>Third-party remote access to CII systems requires enhanced monitoring per CCoP Sections 3.8 and 5.7. ISO 27001 does not exempt the need for: (1) session logging for all remote access, (2) activity monitoring, (3) least privilege access, (4) periodic access review.</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>6.1.4</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>CCoP Section 5.2 requires log retention for forensic investigation, which typically requires longer than 24 hours. Many attacks have dwell time measured in weeks or months. 24-hour retention undermines forensic capability. Six months to one year retention is industry standard for CII.</t>
+          <t>CCoP Section 6.1.4(c) requires log retention for forensic investigation, which typically requires longer than 24 hours. Many attacks have dwell time measured in weeks or months. 24-hour retention undermines forensic capability. Six months to one year retention is industry standard for CII.</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>9.2.1, 9.2.2</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>CCoP Section 6 requires role-specific training. Generic security awareness is insufficient for OT operators who face different threats and work with different systems. Training must be tailored to: (1) OT-specific threats, (2) operational security constraints, (3) emergency response procedures.</t>
+          <t>CCoP Section 9.2 requires role-specific training. Generic security awareness is insufficient for OT operators who face different threats and work with different systems. Training must be tailored to: (1) OT-specific threats, (2) operational security constraints, (3) emergency response procedures.</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.3.1, 7.3.2</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>CCoP Section 8.5 requires incident response plans be tested regularly. An untested plan cannot be relied upon. Annual testing for CII organizations is minimum. Testing validates: (1) contact information accuracy, (2) response procedures, (3) integration with CSA reporting.</t>
+          <t>CCoP Section 7.3 requires incident response plans be tested regularly. An untested plan cannot be relied upon. Annual testing for CII organizations is minimum. Testing validates: (1) contact information accuracy, (2) response procedures, (3) integration with CSA reporting.</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.2.1, 10.2.3</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>5.10.1(d), 5.10.1(e), 5.10.1(g)</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="K72" s="6" t="inlineStr">
         <is>
-          <t>This requires a risk-based decision. CCoP 4.2 requires systems be kept secure. However, warranty preservation may be a valid consideration. The appropriate path: (1) documented risk assessment accepting unpatched state, (2) enhanced isolation, (3) monitoring for exploitation, (4) migration plan.</t>
+          <t>This requires a risk-based decision. CCoP 5.10.1(g) allows compensating controls where a patch cannot be applied. However, warranty preservation may be a valid consideration. The appropriate path: (1) documented risk assessment accepting unpatched state, (2) enhanced isolation, (3) monitoring for exploitation, (4) migration plan.</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>6.4.1, 6.4.3</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>CCoP Section 5.1 requires risk-based security. Sector-specific threat intelligence is a relevant risk factor. Ignoring sector threats until specifically targeted violates the risk-based approach. Enhanced monitoring is appropriate response to credible threat intelligence.</t>
+          <t>CCoP Section 6.4 requires threat-intelligence-driven security. Sector-specific threat intelligence is a relevant risk factor. Ignoring sector threats until specifically targeted violates the risk-based approach. Enhanced monitoring is appropriate response to credible threat intelligence.</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>5.3.1(c) [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
@@ -6266,12 +6266,12 @@
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>8.1.4</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>CCoP Section 9.4 requires backup systems be tested to confirm restoration capability. Documentation alone is insufficient. Testing can be planned during scheduled maintenance to minimize disruption. Untested backups cannot be relied upon during emergencies.</t>
+          <t>CCoP Section 8.1.4 requires backup systems be tested to confirm restoration capability. Documentation alone is insufficient. Testing can be planned during scheduled maintenance to minimize disruption. Untested backups cannot be relied upon during emergencies.</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.15.1, 5.15.3</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>Internal penetration testing provides value but does not fully satisfy CCoP 5.5. CCoP requires independent validation. Internal testers lack objectivity and may have blind spots. CCoP expects external or independent testing at least annually to provide unbiased assessment.</t>
+          <t>Internal penetration testing provides value but does not fully satisfy CCoP 5.15. CCoP requires independent validation. Internal testers lack objectivity and may have blind spots. CCoP expects external or independent testing at least annually to provide unbiased assessment.</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
@@ -6420,12 +6420,12 @@
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>4.1.1, 4.1.2</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>CCoP Section 3 requires current asset inventory. Systems change through: virtual machine creation, cloud deployments, software updates, and configuration changes. Two-year-old inventory cannot be considered accurate. CII requires regular inventory updates at least annually.</t>
+          <t>CCoP Section 4.1 requires current asset inventory. Systems change through: virtual machine creation, cloud deployments, software updates, and configuration changes. Two-year-old inventory cannot be considered accurate. CII requires regular inventory updates at least annually.</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>3.3.1, 3.3.3</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="K78" s="6" t="inlineStr">
         <is>
-          <t>CCoP Section 1 requires documented policies and procedures. Technical controls without policy documentation are not sufficient for compliance. Policies provide: (1) control consistency, (2) staff guidance, (3) audit evidence, (4) continuity when staff change.</t>
+          <t>CCoP Section 3.3 requires documented policies and procedures. Technical controls without policy documentation are not sufficient for compliance. Policies provide: (1) control consistency, (2) staff guidance, (3) audit evidence, (4) continuity when staff change.</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>3.2.5 [support: 2.1.1]</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>1.4.1, 5.1.2</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.4.1, 1.4.5, 1.5.1</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>5.2.3</t>
+          <t>5.1.2, 5.3.1, 5.7.2</t>
         </is>
       </c>
       <c r="I108" s="5" t="inlineStr">
@@ -8822,7 +8822,7 @@
       <c r="J108" s="4" t="n"/>
       <c r="K108" s="6" t="inlineStr">
         <is>
-          <t>According to CCoP 2.0 Section 5.2.3, multi-factor authentication requirements are as follows:
+          <t>According to CCoP 2.0 Section 5.3.1(c), multi-factor authentication requirements are as follows:
 Required for all remote access (critical) Required for privileged accounts (critical) Required for administrative access (critical).
 The intent of this control is to ensure adequate security measures are in place for identity &amp; access management. Organizations must implement controls proportionate to their risk profile while ensuring the core requirements are met.
 Reference: CCoP 2.0, 5.2.3</t>
@@ -9682,12 +9682,12 @@
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>1.6.1, 1.6.2, 1.6.3, 3.2.1 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I119" s="5" t="inlineStr">
@@ -9698,7 +9698,7 @@
       <c r="J119" s="4" t="n"/>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>According to CCoP 2.0 Section 4.3, legacy system exemptions requirements are as follows:
+          <t>According to CCoP 2.0 Section 1.6 (Waiver), legacy system exemptions requirements are as follows:
 No blanket exemptions for legacy (critical) Compensating controls required if not compliant (critical) Must document risk and mitigation plan (important).
 The intent of this control is to ensure adequate security measures are in place for system lifecycle. Organizations must implement controls proportionate to their risk profile while ensuring the core requirements are met.
 Reference: CCoP 2.0, 4.3</t>
@@ -9842,12 +9842,12 @@
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>9.3.1</t>
+          <t>3.8.1, 3.8.2, 3.8.3</t>
         </is>
       </c>
       <c r="I121" s="5" t="inlineStr">
@@ -9858,7 +9858,7 @@
       <c r="J121" s="4" t="n"/>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>According to CCoP 2.0 Section 9.3.1, supply chain control verification requirements are as follows:
+          <t>According to CCoP 2.0 Section 3.8, supply chain control verification requirements are as follows:
 Verify software authenticity and integrity (critical) Source code escrow for critical vendors (important) Vendor security assessment required (critical).
 The intent of this control is to ensure adequate security measures are in place for supply chain security. Organizations must implement controls proportionate to their risk profile while ensuring the core requirements are met.
 Reference: CCoP 2.0, 9.3.1</t>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>5.3.4</t>
+          <t>5.11.1, 5.11.2, 5.11.3, 5.11.4</t>
         </is>
       </c>
       <c r="I122" s="5" t="inlineStr">
@@ -9938,7 +9938,7 @@
       <c r="J122" s="4" t="n"/>
       <c r="K122" s="6" t="inlineStr">
         <is>
-          <t>According to CCoP 2.0 Section 5.3.4, mobile device management requirements are as follows:
+          <t>According to CCoP 2.0 Section 5.11, mobile device management requirements are as follows:
 MDM/EMM solution required (critical) Containerization for corporate data (critical) Remote wipe capability mandatory (important).
 The intent of this control is to ensure adequate security measures are in place for endpoint security. Organizations must implement controls proportionate to their risk profile while ensuring the core requirements are met.
 Reference: CCoP 2.0, 5.3.4</t>
@@ -10127,7 +10127,11 @@
       <c r="P124" s="7" t="n"/>
       <c r="Q124" s="7" t="n"/>
       <c r="R124" s="7" t="n"/>
-      <c r="S124" s="7" t="n"/>
+      <c r="S124" s="7" t="inlineStr">
+        <is>
+          <t>[DEPRECATED: Cross-border data transfer scoped to PDPA, not CCoP 2.0]</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="195" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
@@ -10167,7 +10171,7 @@
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>5.2.3</t>
+          <t>5.1.2, 5.3.1, 5.7.2</t>
         </is>
       </c>
       <c r="I125" s="5" t="inlineStr">
@@ -10178,7 +10182,7 @@
       <c r="J125" s="4" t="n"/>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>According to CCoP 2.0 Section 5.2.3, mfa not required internally requirements are as follows:
+          <t>According to CCoP 2.0 Section 5.3.1(c), mfa not required internally requirements are as follows:
 Isolated networks still require MFA (critical) Network isolation is a control, not a waiver (important) All privileged access requires MFA regardless (critical).
 The intent of this control is to ensure adequate security measures are in place for identity &amp; access management. Organizations must implement controls proportionate to their risk profile while ensuring the core requirements are met.
 Reference: CCoP 2.0, 5.2.3</t>
@@ -10806,7 +10810,7 @@
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>5.2.3</t>
+          <t>5.1.2, 5.3.1, 5.7.2</t>
         </is>
       </c>
       <c r="I133" s="5" t="inlineStr">
@@ -10817,7 +10821,7 @@
       <c r="J133" s="4" t="n"/>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>The primary security intent of CCoP 2.0 Section 5.2.3 regarding mfa - preventing credential theft impact is: Limit impact of compromised credentials through defense in depth.
+          <t>The primary security intent of CCoP 2.0 Section 5.3.1(c) regarding mfa - preventing credential theft impact is: Limit impact of compromised credentials through defense in depth.
 This intent is achieved through:
 - Single factor compromise insufficient for access (critical)
 - Protects against phishing and credential theft (critical)
@@ -11719,7 +11723,7 @@
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>5.2.5</t>
+          <t>5.2.1, 5.2.2</t>
         </is>
       </c>
       <c r="I144" s="5" t="inlineStr">
@@ -11730,7 +11734,7 @@
       <c r="J144" s="4" t="n"/>
       <c r="K144" s="6" t="inlineStr">
         <is>
-          <t>The primary security intent of CCoP 2.0 Section 5.2.5 regarding access review - privilege creep prevention is: Prevent privilege accumulation beyond actual need.
+          <t>The primary security intent of CCoP 2.0 Section 5.2.2 regarding access review - privilege creep prevention is: Prevent privilege accumulation beyond actual need.
 This intent is achieved through:
 - Users accumulate access over time without losing old rights (critical)
 - Excessive access increases breach impact (critical)
@@ -12129,12 +12133,12 @@
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>7.4.1</t>
+          <t>8.2.1, 8.2.2</t>
         </is>
       </c>
       <c r="I149" s="5" t="inlineStr">
@@ -12145,7 +12149,7 @@
       <c r="J149" s="4" t="n"/>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>The primary security intent of CCoP 2.0 Section 7.4.1 regarding business continuity - resilience is: Ensure essential functions despite successful cyber attacks.
+          <t>The primary security intent of CCoP 2.0 Section 8.2 regarding business continuity - resilience is: Ensure essential functions despite successful cyber attacks.
 This intent is achieved through:
 - Controls may fail despite best efforts (critical)
 - BCP provides recovery path when prevention fails (critical)
@@ -12212,12 +12216,12 @@
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.1, 3.2.2 [support: Risk Assessment Guide §3]</t>
         </is>
       </c>
       <c r="I150" s="5" t="inlineStr">
@@ -12228,7 +12232,7 @@
       <c r="J150" s="4" t="n"/>
       <c r="K150" s="6" t="inlineStr">
         <is>
-          <t>The primary security intent of CCoP 2.0 Section 4.2.1 regarding risk assessment - informed decision making is: Enable security investment decisions based on measured risk.
+          <t>The primary security intent of CCoP 2.0 Section 3.2 regarding risk assessment - informed decision making is: Enable security investment decisions based on measured risk.
 This intent is achieved through:
 - Resources are finite and must be allocated efficiently (critical)
 - Risk assessment identifies highest-priority vulnerabilities (critical)
@@ -12378,12 +12382,12 @@
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>4.2.2</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I152" s="5" t="inlineStr">
@@ -12396,7 +12400,7 @@
         <is>
           <t>Based on the scenario 'Incomplete CII asset inventory', the following compliance gaps are identified:
 **Gap Type:** Missing Control
-**CCoP Reference:** Section 4.2.2
+**CCoP Reference:** Section 3.2.2(b) / 3.2.2(c)
 **Key Gaps:**
 - OT systems within CII scope must be inventoried (critical priority)
 - Incomplete inventory prevents comprehensive risk assessment (critical priority)
@@ -12406,7 +12410,7 @@
 2. Implement compensating controls if immediate remediation not feasible
 3. Establish ongoing monitoring to prevent recurrence
 **Risk Level:** High
-Reference: CCoP 2.0, 4.2.2</t>
+Reference: CCoP 2.0, 3.2.2(b) / 3.2.2(c)</t>
         </is>
       </c>
       <c r="L152" s="4" t="inlineStr">
@@ -12467,12 +12471,12 @@
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>4.2.2</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I153" s="5" t="inlineStr">
@@ -12485,7 +12489,7 @@
         <is>
           <t>Based on the scenario 'Missing shadow IT inventory', the following compliance gaps are identified:
 **Gap Type:** Missing Control
-**CCoP Reference:** Section 4.2.2
+**CCoP Reference:** Section 3.2.2(b) / 3.2.2(c)
 **Key Gaps:**
 - Shadow IT creates unmonitored attack surface (critical priority)
 - Data exposure risk outside approved controls (critical priority)
@@ -12495,7 +12499,7 @@
 2. Implement compensating controls if immediate remediation not feasible
 3. Establish ongoing monitoring to prevent recurrence
 **Risk Level:** High
-Reference: CCoP 2.0, 4.2.2</t>
+Reference: CCoP 2.0, 3.2.2(b) / 3.2.2(c)</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">
@@ -12556,12 +12560,12 @@
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>4.2.2</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I154" s="5" t="inlineStr">
@@ -12574,7 +12578,7 @@
         <is>
           <t>Based on the scenario 'Outdated asset inventory', the following compliance gaps are identified:
 **Gap Type:** Inadequate Implementation
-**CCoP Reference:** Section 4.2.2
+**CCoP Reference:** Section 3.2.2(b) / 3.2.2(c)
 **Key Gaps:**
 - Inventory must reflect current operational state (critical priority)
 - Decommissioned systems shouldn't be monitored as active (important priority)
@@ -12584,7 +12588,7 @@
 2. Implement compensating controls if immediate remediation not feasible
 3. Establish ongoing monitoring to prevent recurrence
 **Risk Level:** High
-Reference: CCoP 2.0, 4.2.2</t>
+Reference: CCoP 2.0, 3.2.2(b) / 3.2.2(c)</t>
         </is>
       </c>
       <c r="L154" s="4" t="inlineStr">
@@ -12734,12 +12738,12 @@
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>4.2.2</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I156" s="5" t="inlineStr">
@@ -12752,7 +12756,7 @@
         <is>
           <t>Based on the scenario 'Data flow mapping incomplete', the following compliance gaps are identified:
 **Gap Type:** Inadequate Implementation
-**CCoP Reference:** Section 4.2.2
+**CCoP Reference:** Section 3.2.2(b) / 3.2.2(c)
 **Key Gaps:**
 - Data flow maps required for boundary definition (critical priority)
 - Undocumented flows create unprotected data paths (critical priority)
@@ -12762,7 +12766,7 @@
 2. Implement compensating controls if immediate remediation not feasible
 3. Establish ongoing monitoring to prevent recurrence
 **Risk Level:** High
-Reference: CCoP 2.0, 4.2.2</t>
+Reference: CCoP 2.0, 3.2.2(b) / 3.2.2(c)</t>
         </is>
       </c>
       <c r="L156" s="4" t="inlineStr">
@@ -12828,7 +12832,7 @@
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>5.2.4</t>
+          <t>5.2.1, 5.3.1</t>
         </is>
       </c>
       <c r="I157" s="5" t="inlineStr">
@@ -12841,7 +12845,7 @@
         <is>
           <t>Based on the scenario 'Shared admin accounts', the following compliance gaps are identified:
 **Gap Type:** Missing Control
-**CCoP Reference:** Section 5.2.4
+**CCoP Reference:** Section 5.2.1(c)
 **Key Gaps:**
 - Shared accounts prevent individual accountability (critical priority)
 - Logs cannot definitively attribute actions to individuals (critical priority)
@@ -12917,7 +12921,7 @@
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>5.2.5</t>
+          <t>5.2.2, 5.3.1</t>
         </is>
       </c>
       <c r="I158" s="5" t="inlineStr">
@@ -12930,7 +12934,7 @@
         <is>
           <t>Based on the scenario 'No privileged access review', the following compliance gaps are identified:
 **Gap Type:** Missing Control
-**CCoP Reference:** Section 5.2.5
+**CCoP Reference:** Section 5.2.2
 **Key Gaps:**
 - Periodic access review mandatory for privileged accounts (critical priority)
 - Privilege creep creates excessive exposure (critical priority)
@@ -13006,7 +13010,7 @@
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>5.2.4</t>
+          <t>5.2.1, 5.3.1</t>
         </is>
       </c>
       <c r="I159" s="5" t="inlineStr">
@@ -13019,7 +13023,7 @@
         <is>
           <t>Based on the scenario 'Service accounts with excessive permissions', the following compliance gaps are identified:
 **Gap Type:** Inadequate Implementation
-**CCoP Reference:** Section 5.2.4
+**CCoP Reference:** Section 5.2.1(a)
 **Key Gaps:**
 - Service accounts must have least privileged access (critical priority)
 - Domain admin level unjustified for application service (critical priority)
@@ -13180,7 +13184,7 @@
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>5.2.6</t>
+          <t>5.3.1</t>
         </is>
       </c>
       <c r="I161" s="5" t="inlineStr">
@@ -13193,7 +13197,7 @@
         <is>
           <t>Based on the scenario 'Break-glass procedure undefined', the following compliance gaps are identified:
 **Gap Type:** Missing Control
-**CCoP Reference:** Section 5.2.6
+**CCoP Reference:** Section 5.3.1
 **Key Gaps:**
 - Emergency access must have documented procedures (critical priority)
 - Post-emergency review required to detect misuse (critical priority)
@@ -13621,7 +13625,7 @@
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>6.3.4</t>
+          <t>6.2.1, 6.2.2, 6.2.3</t>
         </is>
       </c>
       <c r="I166" s="5" t="inlineStr">
@@ -13634,7 +13638,7 @@
         <is>
           <t>Based on the scenario 'Alerting threshold too high', the following compliance gaps are identified:
 **Gap Type:** Inadequate Implementation
-**CCoP Reference:** Section 6.3.4
+**CCoP Reference:** Section 6.2
 **Key Gaps:**
 - Alert tuning must balance noise reduction with detection sensitivity (critical priority)
 - Over-tuning creates detection blind spots (critical priority)
@@ -13799,7 +13803,7 @@
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>5.5.1, 5.5.2, 10.2.1</t>
         </is>
       </c>
       <c r="I168" s="5" t="inlineStr">
@@ -13812,7 +13816,7 @@
         <is>
           <t>Based on the scenario 'OT flat network', the following compliance gaps are identified:
 **Gap Type:** Missing Control
-**CCoP Reference:** Section 5.4.2
+**CCoP Reference:** Section 5.5
 **Key Gaps:**
 - OT networks require segmentation to limit blast radius (critical priority)
 - Flat networks enable lateral movement (critical priority)
@@ -13884,7 +13888,7 @@
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
-          <t>5.4.4</t>
+          <t>5.7.1, 5.7.2, 10.2.3</t>
         </is>
       </c>
       <c r="I169" s="5" t="inlineStr">
@@ -13897,7 +13901,7 @@
         <is>
           <t>Based on the scenario 'Remote OT access unprotected', the following compliance gaps are identified:
 **Gap Type:** Missing Control
-**CCoP Reference:** Section 5.4.4
+**CCoP Reference:** Section 5.7
 **Key Gaps:**
 - Remote OT access must be through controlled jump hosts (critical priority)
 - Direct vendor connection bypasses security monitoring (critical priority)
@@ -14673,7 +14677,7 @@
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
-          <t>5.2.3</t>
+          <t>5.1.2, 5.7.2</t>
         </is>
       </c>
       <c r="I178" s="5" t="inlineStr">
@@ -14686,7 +14690,7 @@
         <is>
           <t>Based on the scenario 'Policy: MFA required / Practice: exceptions granted broadly', the following compliance gaps are identified:
 **Gap Type:** Policy Practice Gap
-**CCoP Reference:** Section 5.2.3
+**CCoP Reference:** Section 5.7.2
 **Key Gaps:**
 - Broad exemptions undermine control effectiveness (critical priority)
 - 40% exception rate indicates control failure, not legitimate exceptions (critical priority)
@@ -15024,12 +15028,12 @@
       </c>
       <c r="G182" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I182" s="5" t="inlineStr">
@@ -15060,7 +15064,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L182" s="4" t="inlineStr">
@@ -15121,12 +15125,12 @@
       </c>
       <c r="G183" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I183" s="5" t="inlineStr">
@@ -15157,7 +15161,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L183" s="4" t="inlineStr">
@@ -15218,12 +15222,12 @@
       </c>
       <c r="G184" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I184" s="5" t="inlineStr">
@@ -15253,7 +15257,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L184" s="4" t="inlineStr">
@@ -15314,12 +15318,12 @@
       </c>
       <c r="G185" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I185" s="5" t="inlineStr">
@@ -15349,7 +15353,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L185" s="4" t="inlineStr">
@@ -15410,12 +15414,12 @@
       </c>
       <c r="G186" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I186" s="5" t="inlineStr">
@@ -15445,7 +15449,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L186" s="4" t="inlineStr">
@@ -15506,12 +15510,12 @@
       </c>
       <c r="G187" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I187" s="5" t="inlineStr">
@@ -15541,7 +15545,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L187" s="4" t="inlineStr">
@@ -15602,12 +15606,12 @@
       </c>
       <c r="G188" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I188" s="5" t="inlineStr">
@@ -15638,7 +15642,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L188" s="4" t="inlineStr">
@@ -15699,12 +15703,12 @@
       </c>
       <c r="G189" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I189" s="5" t="inlineStr">
@@ -15735,7 +15739,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L189" s="4" t="inlineStr">
@@ -15796,12 +15800,12 @@
       </c>
       <c r="G190" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I190" s="5" t="inlineStr">
@@ -15832,7 +15836,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L190" s="4" t="inlineStr">
@@ -15893,12 +15897,12 @@
       </c>
       <c r="G191" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I191" s="5" t="inlineStr">
@@ -15929,7 +15933,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L191" s="4" t="inlineStr">
@@ -15990,12 +15994,12 @@
       </c>
       <c r="G192" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I192" s="5" t="inlineStr">
@@ -16026,7 +16030,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L192" s="4" t="inlineStr">
@@ -16087,12 +16091,12 @@
       </c>
       <c r="G193" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I193" s="5" t="inlineStr">
@@ -16123,7 +16127,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L193" s="4" t="inlineStr">
@@ -16184,12 +16188,12 @@
       </c>
       <c r="G194" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I194" s="5" t="inlineStr">
@@ -16220,7 +16224,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L194" s="4" t="inlineStr">
@@ -16281,12 +16285,12 @@
       </c>
       <c r="G195" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I195" s="5" t="inlineStr">
@@ -16317,7 +16321,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L195" s="4" t="inlineStr">
@@ -16378,12 +16382,12 @@
       </c>
       <c r="G196" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I196" s="5" t="inlineStr">
@@ -16414,7 +16418,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L196" s="4" t="inlineStr">
@@ -16475,12 +16479,12 @@
       </c>
       <c r="G197" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I197" s="5" t="inlineStr">
@@ -16511,7 +16515,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L197" s="4" t="inlineStr">
@@ -16572,12 +16576,12 @@
       </c>
       <c r="G198" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I198" s="5" t="inlineStr">
@@ -16608,7 +16612,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L198" s="4" t="inlineStr">
@@ -16669,12 +16673,12 @@
       </c>
       <c r="G199" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I199" s="5" t="inlineStr">
@@ -16706,7 +16710,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L199" s="4" t="inlineStr">
@@ -16767,12 +16771,12 @@
       </c>
       <c r="G200" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I200" s="5" t="inlineStr">
@@ -16804,7 +16808,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L200" s="4" t="inlineStr">
@@ -16865,12 +16869,12 @@
       </c>
       <c r="G201" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I201" s="5" t="inlineStr">
@@ -16902,7 +16906,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L201" s="4" t="inlineStr">
@@ -16963,12 +16967,12 @@
       </c>
       <c r="G202" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I202" s="5" t="inlineStr">
@@ -17000,7 +17004,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L202" s="4" t="inlineStr">
@@ -17061,12 +17065,12 @@
       </c>
       <c r="G203" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I203" s="5" t="inlineStr">
@@ -17098,7 +17102,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L203" s="4" t="inlineStr">
@@ -17159,12 +17163,12 @@
       </c>
       <c r="G204" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I204" s="5" t="inlineStr">
@@ -17196,7 +17200,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L204" s="4" t="inlineStr">
@@ -17257,12 +17261,12 @@
       </c>
       <c r="G205" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I205" s="5" t="inlineStr">
@@ -17294,7 +17298,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L205" s="4" t="inlineStr">
@@ -17355,12 +17359,12 @@
       </c>
       <c r="G206" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(b), 3.2.2(c) [support: Risk Assessment Guide §4.2, §4.3]</t>
         </is>
       </c>
       <c r="I206" s="5" t="inlineStr">
@@ -17392,7 +17396,7 @@
 2. High likelihood + High effort + Low effort alternatives exist = Quick wins first
 3. Safety-critical OT &gt; Availability &gt; Confidentiality for OT systems
 4. Regulatory deadline-driven items when applicable
-Reference: CCoP 2.0 Sections 4.2 (risk assessment), 7.1 (incident classification)</t>
+Reference: CCoP 2.0 Section 3.2.2 (risk assessment methodology); Risk Assessment Guide §4.2 Risk Analysis; §4.3 Risk Evaluation, 7.1 (incident classification)</t>
         </is>
       </c>
       <c r="L206" s="4" t="inlineStr">
@@ -17453,12 +17457,12 @@
       </c>
       <c r="G207" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I207" s="5" t="inlineStr">
@@ -17549,12 +17553,12 @@
       </c>
       <c r="G208" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I208" s="5" t="inlineStr">
@@ -17641,12 +17645,12 @@
       </c>
       <c r="G209" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I209" s="5" t="inlineStr">
@@ -17737,12 +17741,12 @@
       </c>
       <c r="G210" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I210" s="5" t="inlineStr">
@@ -17833,12 +17837,12 @@
       </c>
       <c r="G211" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I211" s="5" t="inlineStr">
@@ -17925,12 +17929,12 @@
       </c>
       <c r="G212" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I212" s="5" t="inlineStr">
@@ -18021,12 +18025,12 @@
       </c>
       <c r="G213" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I213" s="5" t="inlineStr">
@@ -18117,12 +18121,12 @@
       </c>
       <c r="G214" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I214" s="5" t="inlineStr">
@@ -18213,12 +18217,12 @@
       </c>
       <c r="G215" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I215" s="5" t="inlineStr">
@@ -18309,12 +18313,12 @@
       </c>
       <c r="G216" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I216" s="5" t="inlineStr">
@@ -18405,12 +18409,12 @@
       </c>
       <c r="G217" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I217" s="5" t="inlineStr">
@@ -18501,12 +18505,12 @@
       </c>
       <c r="G218" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I218" s="5" t="inlineStr">
@@ -18597,12 +18601,12 @@
       </c>
       <c r="G219" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I219" s="5" t="inlineStr">
@@ -18693,12 +18697,12 @@
       </c>
       <c r="G220" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I220" s="5" t="inlineStr">
@@ -18786,12 +18790,12 @@
       </c>
       <c r="G221" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I221" s="5" t="inlineStr">
@@ -18879,12 +18883,12 @@
       </c>
       <c r="G222" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I222" s="5" t="inlineStr">
@@ -18972,12 +18976,12 @@
       </c>
       <c r="G223" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I223" s="5" t="inlineStr">
@@ -19065,12 +19069,12 @@
       </c>
       <c r="G224" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I224" s="5" t="inlineStr">
@@ -19158,12 +19162,12 @@
       </c>
       <c r="G225" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I225" s="5" t="inlineStr">
@@ -19251,12 +19255,12 @@
       </c>
       <c r="G226" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I226" s="5" t="inlineStr">
@@ -19344,12 +19348,12 @@
       </c>
       <c r="G227" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I227" s="5" t="inlineStr">
@@ -19437,12 +19441,12 @@
       </c>
       <c r="G228" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I228" s="5" t="inlineStr">
@@ -19530,12 +19534,12 @@
       </c>
       <c r="G229" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I229" s="5" t="inlineStr">
@@ -19623,12 +19627,12 @@
       </c>
       <c r="G230" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I230" s="5" t="inlineStr">
@@ -19716,12 +19720,12 @@
       </c>
       <c r="G231" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.2(a), 3.2.4, 3.2.5 [support: Risk Assessment Guide §4.1]</t>
         </is>
       </c>
       <c r="I231" s="5" t="inlineStr">
@@ -21646,7 +21650,7 @@
       </c>
       <c r="H252" s="4" t="inlineStr">
         <is>
-          <t>5.2.3</t>
+          <t>5.1.2, 5.3.1, 5.7.2 [support: Auditing Guidelines for CII]</t>
         </is>
       </c>
       <c r="I252" s="5" t="inlineStr">
@@ -21659,7 +21663,7 @@
         <is>
           <t>**Audit Perspective: Multi-factor authentication**
 **CSA Auditor Viewpoint:**
-When assessing multi-factor authentication under CCoP 2.0 5.2.3, a CSA auditor would examine:
+When assessing multi-factor authentication under CCoP 2.0 §5.3.1(c), a CSA auditor would examine:
 - Control implementation against the clause requirements
 - Evidence of effective operation, not just documentation
 - Coverage across all applicable systems and personnel
@@ -21671,7 +21675,7 @@
 - Risk Manager: inventory MFA deployment, identify gaps before audit (important priority)
 **Key Insight:**
 Auditors look for evidence that controls are operational and effective, not just documented. Risk Managers should focus on demonstrating control effectiveness through observable evidence.
-Reference: CCoP 2.0 5.2.3, CIIO Audit Process</t>
+Reference: CCoP 2.0 §5.3.1(c), CIIO Audit Process</t>
         </is>
       </c>
       <c r="L252" s="4" t="inlineStr">
@@ -22010,7 +22014,7 @@
       </c>
       <c r="H256" s="4" t="inlineStr">
         <is>
-          <t>4.2.2</t>
+          <t>4.1.1, 4.1.2 [support: Auditing Guidelines for CII]</t>
         </is>
       </c>
       <c r="I256" s="5" t="inlineStr">
@@ -22023,7 +22027,7 @@
         <is>
           <t>**Audit Perspective: Asset inventory completeness**
 **CSA Auditor Viewpoint:**
-When assessing asset inventory completeness under CCoP 2.0 4.2.2, a CSA auditor would examine:
+When assessing asset inventory completeness under CCoP 2.0 §4.1, a CSA auditor would examine:
 - Control implementation against the clause requirements
 - Evidence of effective operation, not just documentation
 - Coverage across all applicable systems and personnel
@@ -22035,7 +22039,7 @@
 - Risk Manager: ensure inventory current and cross-referenced with network scans (important priority)
 **Key Insight:**
 Auditors look for evidence that controls are operational and effective, not just documented. Risk Managers should focus on demonstrating control effectiveness through observable evidence.
-Reference: CCoP 2.0 4.2.2, CIIO Audit Process</t>
+Reference: CCoP 2.0 §4.1, CIIO Audit Process</t>
         </is>
       </c>
       <c r="L256" s="4" t="inlineStr">
@@ -22278,12 +22282,12 @@
       </c>
       <c r="G259" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr">
         <is>
-          <t>7.4.1</t>
+          <t>8.2.1, 8.2.2, 8.2.3, 8.2.4 [support: Auditing Guidelines for CII]</t>
         </is>
       </c>
       <c r="I259" s="5" t="inlineStr">
@@ -22296,7 +22300,7 @@
         <is>
           <t>**Audit Perspective: Business continuity planning**
 **CSA Auditor Viewpoint:**
-When assessing business continuity planning under CCoP 2.0 7.4.1, a CSA auditor would examine:
+When assessing business continuity planning under CCoP 2.0 §8.2, a CSA auditor would examine:
 - Control implementation against the clause requirements
 - Evidence of effective operation, not just documentation
 - Coverage across all applicable systems and personnel
@@ -22308,7 +22312,7 @@
 - Risk Manager: ensure BCP tested within last year, RTO/RPO defined for critical systems (important priority)
 **Key Insight:**
 Auditors look for evidence that controls are operational and effective, not just documented. Risk Managers should focus on demonstrating control effectiveness through observable evidence.
-Reference: CCoP 2.0 7.4.1, CIIO Audit Process</t>
+Reference: CCoP 2.0 §8.2, CIIO Audit Process</t>
         </is>
       </c>
       <c r="L259" s="4" t="inlineStr">
@@ -22829,7 +22833,7 @@
       </c>
       <c r="H265" s="4" t="inlineStr">
         <is>
-          <t>5.2.5</t>
+          <t>5.2.1, 5.2.2 [support: Auditing Guidelines for CII]</t>
         </is>
       </c>
       <c r="I265" s="5" t="inlineStr">
@@ -22842,7 +22846,7 @@
         <is>
           <t>**Audit Perspective: Access control review process**
 **CSA Auditor Viewpoint:**
-When assessing access control review process under CCoP 2.0 5.2.5, a CSA auditor would examine:
+When assessing access control review process under CCoP 2.0 §5.2.2, a CSA auditor would examine:
 - Control implementation against the clause requirements
 - Evidence of effective operation, not just documentation
 - Coverage across all applicable systems and personnel
@@ -22854,7 +22858,7 @@
 - Risk Manager: ensure reviews quarterly for privileged accounts, annual for all staff (important priority)
 **Key Insight:**
 Auditors look for evidence that controls are operational and effective, not just documented. Risk Managers should focus on demonstrating control effectiveness through observable evidence.
-Reference: CCoP 2.0 5.2.5, CIIO Audit Process</t>
+Reference: CCoP 2.0 §5.2.2, CIIO Audit Process</t>
         </is>
       </c>
       <c r="L265" s="4" t="inlineStr">
@@ -23002,12 +23006,12 @@
       </c>
       <c r="G267" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr">
         <is>
-          <t>9.3.1</t>
+          <t>3.8.1, 3.8.2, 3.8.3, 3.8.4, 3.8.5 [support: Auditing Guidelines for CII]</t>
         </is>
       </c>
       <c r="I267" s="5" t="inlineStr">
@@ -23020,7 +23024,7 @@
         <is>
           <t>**Audit Perspective: Supply chain security management**
 **CSA Auditor Viewpoint:**
-When assessing supply chain security management under CCoP 2.0 9.3.1, a CSA auditor would examine:
+When assessing supply chain security management under CCoP 2.0 §3.8, a CSA auditor would examine:
 - Control implementation against the clause requirements
 - Evidence of effective operation, not just documentation
 - Coverage across all applicable systems and personnel
@@ -23032,7 +23036,7 @@
 - Risk Manager: ensure all software and hardware procurement includes security assessment (important priority)
 **Key Insight:**
 Auditors look for evidence that controls are operational and effective, not just documented. Risk Managers should focus on demonstrating control effectiveness through observable evidence.
-Reference: CCoP 2.0 9.3.1, CIIO Audit Process</t>
+Reference: CCoP 2.0 §3.8, CIIO Audit Process</t>
         </is>
       </c>
       <c r="L267" s="4" t="inlineStr">
@@ -23354,12 +23358,12 @@
       </c>
       <c r="G271" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.2.1, 3.2.2 [support: Auditing Guidelines for CII, Risk Assessment Guide §3]</t>
         </is>
       </c>
       <c r="I271" s="5" t="inlineStr">
@@ -23372,7 +23376,7 @@
         <is>
           <t>**Audit Perspective: Risk-based vs compliance-based methodology**
 **CSA Auditor Viewpoint:**
-When assessing risk-based vs compliance-based methodology under CCoP 2.0 4.2.1, a CSA auditor would examine:
+When assessing risk-based vs compliance-based methodology under CCoP 2.0 §3.2, a CSA auditor would examine:
 - Control implementation against the clause requirements
 - Evidence of effective operation, not just documentation
 - Coverage across all applicable systems and personnel
@@ -23384,7 +23388,7 @@
 - Risk Manager: demonstrate clear link between risk assessment and control implementation
 **Key Insight:**
 Auditors look for evidence that controls are operational and effective, not just documented. Risk Managers should focus on demonstrating control effectiveness through observable evidence.
-Reference: CCoP 2.0 4.2.1, CIIO Audit Process</t>
+Reference: CCoP 2.0 §3.2, CIIO Audit Process</t>
         </is>
       </c>
       <c r="L271" s="4" t="inlineStr">
@@ -30716,7 +30720,11 @@
       <c r="P347" s="7" t="n"/>
       <c r="Q347" s="7" t="n"/>
       <c r="R347" s="7" t="n"/>
-      <c r="S347" s="7" t="n"/>
+      <c r="S347" s="7" t="inlineStr">
+        <is>
+          <t>[AUDIT_EXEMPT: hallucination benchmark — by design]</t>
+        </is>
+      </c>
     </row>
     <row r="348" ht="150" customHeight="1">
       <c r="A348" s="4" t="inlineStr">
@@ -30947,7 +30955,11 @@
       <c r="P350" s="7" t="n"/>
       <c r="Q350" s="7" t="n"/>
       <c r="R350" s="7" t="n"/>
-      <c r="S350" s="7" t="n"/>
+      <c r="S350" s="7" t="inlineStr">
+        <is>
+          <t>[AUDIT_EXEMPT: hallucination benchmark — by design]</t>
+        </is>
+      </c>
     </row>
     <row r="351" ht="150" customHeight="1">
       <c r="A351" s="4" t="inlineStr">
@@ -31024,7 +31036,11 @@
       <c r="P351" s="7" t="n"/>
       <c r="Q351" s="7" t="n"/>
       <c r="R351" s="7" t="n"/>
-      <c r="S351" s="7" t="n"/>
+      <c r="S351" s="7" t="inlineStr">
+        <is>
+          <t>[AUDIT_EXEMPT: hallucination benchmark — by design]</t>
+        </is>
+      </c>
     </row>
     <row r="352" ht="150" customHeight="1">
       <c r="A352" s="4" t="inlineStr">
@@ -31255,7 +31271,11 @@
       <c r="P354" s="7" t="n"/>
       <c r="Q354" s="7" t="n"/>
       <c r="R354" s="7" t="n"/>
-      <c r="S354" s="7" t="n"/>
+      <c r="S354" s="7" t="inlineStr">
+        <is>
+          <t>[AUDIT_EXEMPT: hallucination benchmark — by design]</t>
+        </is>
+      </c>
     </row>
     <row r="355" ht="165" customHeight="1">
       <c r="A355" s="4" t="inlineStr">
@@ -31332,7 +31352,11 @@
       <c r="P355" s="7" t="n"/>
       <c r="Q355" s="7" t="n"/>
       <c r="R355" s="7" t="n"/>
-      <c r="S355" s="7" t="n"/>
+      <c r="S355" s="7" t="inlineStr">
+        <is>
+          <t>[AUDIT_EXEMPT: hallucination benchmark — by design]</t>
+        </is>
+      </c>
     </row>
     <row r="356" ht="165" customHeight="1">
       <c r="A356" s="4" t="inlineStr">
@@ -31409,7 +31433,11 @@
       <c r="P356" s="7" t="n"/>
       <c r="Q356" s="7" t="n"/>
       <c r="R356" s="7" t="n"/>
-      <c r="S356" s="7" t="n"/>
+      <c r="S356" s="7" t="inlineStr">
+        <is>
+          <t>[AUDIT_EXEMPT: hallucination benchmark — by design]</t>
+        </is>
+      </c>
     </row>
     <row r="357" ht="165" customHeight="1">
       <c r="A357" s="4" t="inlineStr">
@@ -31563,7 +31591,11 @@
       <c r="P358" s="7" t="n"/>
       <c r="Q358" s="7" t="n"/>
       <c r="R358" s="7" t="n"/>
-      <c r="S358" s="7" t="n"/>
+      <c r="S358" s="7" t="inlineStr">
+        <is>
+          <t>[AUDIT_EXEMPT: hallucination benchmark — by design]</t>
+        </is>
+      </c>
     </row>
     <row r="359" ht="165" customHeight="1">
       <c r="A359" s="4" t="inlineStr">
@@ -31871,7 +31903,11 @@
       <c r="P362" s="7" t="n"/>
       <c r="Q362" s="7" t="n"/>
       <c r="R362" s="7" t="n"/>
-      <c r="S362" s="7" t="n"/>
+      <c r="S362" s="7" t="inlineStr">
+        <is>
+          <t>[AUDIT_EXEMPT: hallucination benchmark — by design]</t>
+        </is>
+      </c>
     </row>
     <row r="363" ht="135" customHeight="1">
       <c r="A363" s="4" t="inlineStr">
@@ -32025,7 +32061,11 @@
       <c r="P364" s="7" t="n"/>
       <c r="Q364" s="7" t="n"/>
       <c r="R364" s="7" t="n"/>
-      <c r="S364" s="7" t="n"/>
+      <c r="S364" s="7" t="inlineStr">
+        <is>
+          <t>[AUDIT_EXEMPT: hallucination benchmark — by design]</t>
+        </is>
+      </c>
     </row>
     <row r="365" ht="150" customHeight="1">
       <c r="A365" s="4" t="inlineStr">
@@ -32102,7 +32142,11 @@
       <c r="P365" s="7" t="n"/>
       <c r="Q365" s="7" t="n"/>
       <c r="R365" s="7" t="n"/>
-      <c r="S365" s="7" t="n"/>
+      <c r="S365" s="7" t="inlineStr">
+        <is>
+          <t>[AUDIT_EXEMPT: hallucination benchmark — by design]</t>
+        </is>
+      </c>
     </row>
     <row r="366" ht="150" customHeight="1">
       <c r="A366" s="4" t="inlineStr">
@@ -32256,7 +32300,11 @@
       <c r="P367" s="7" t="n"/>
       <c r="Q367" s="7" t="n"/>
       <c r="R367" s="7" t="n"/>
-      <c r="S367" s="7" t="n"/>
+      <c r="S367" s="7" t="inlineStr">
+        <is>
+          <t>[AUDIT_EXEMPT: hallucination benchmark — by design]</t>
+        </is>
+      </c>
     </row>
     <row r="368" ht="150" customHeight="1">
       <c r="A368" s="4" t="inlineStr">
@@ -32599,12 +32647,12 @@
       </c>
       <c r="G372" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I372" s="5" t="inlineStr">
@@ -32693,12 +32741,12 @@
       </c>
       <c r="G373" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I373" s="5" t="inlineStr">
@@ -32787,12 +32835,12 @@
       </c>
       <c r="G374" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I374" s="5" t="inlineStr">
@@ -32881,12 +32929,12 @@
       </c>
       <c r="G375" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I375" s="5" t="inlineStr">
@@ -32975,12 +33023,12 @@
       </c>
       <c r="G376" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I376" s="5" t="inlineStr">
@@ -33069,12 +33117,12 @@
       </c>
       <c r="G377" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I377" s="5" t="inlineStr">
@@ -33159,12 +33207,12 @@
       </c>
       <c r="G378" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I378" s="5" t="inlineStr">
@@ -33253,12 +33301,12 @@
       </c>
       <c r="G379" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I379" s="5" t="inlineStr">
@@ -33347,12 +33395,12 @@
       </c>
       <c r="G380" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I380" s="5" t="inlineStr">
@@ -33441,12 +33489,12 @@
       </c>
       <c r="G381" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I381" s="5" t="inlineStr">
@@ -33535,12 +33583,12 @@
       </c>
       <c r="G382" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I382" s="5" t="inlineStr">
@@ -33629,12 +33677,12 @@
       </c>
       <c r="G383" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I383" s="5" t="inlineStr">
@@ -33719,12 +33767,12 @@
       </c>
       <c r="G384" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I384" s="5" t="inlineStr">
@@ -33813,12 +33861,12 @@
       </c>
       <c r="G385" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I385" s="5" t="inlineStr">
@@ -33907,12 +33955,12 @@
       </c>
       <c r="G386" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I386" s="5" t="inlineStr">
@@ -33997,12 +34045,12 @@
       </c>
       <c r="G387" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I387" s="5" t="inlineStr">
@@ -34091,12 +34139,12 @@
       </c>
       <c r="G388" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I388" s="5" t="inlineStr">
@@ -34185,12 +34233,12 @@
       </c>
       <c r="G389" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I389" s="5" t="inlineStr">
@@ -34279,12 +34327,12 @@
       </c>
       <c r="G390" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I390" s="5" t="inlineStr">
@@ -34373,12 +34421,12 @@
       </c>
       <c r="G391" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>1.6.1, 1.6.2, 1.6.3 [support: Cybersecurity Act 2018 §11(7)]</t>
         </is>
       </c>
       <c r="I391" s="5" t="inlineStr">
@@ -36415,12 +36463,12 @@
       </c>
       <c r="G412" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr">
         <is>
-          <t>8.2,8.4</t>
+          <t>7.1.1(b), 7.1.1(g), 7.1.1(h) [support: 8.2.1]</t>
         </is>
       </c>
       <c r="I412" s="5" t="inlineStr">
@@ -36484,12 +36532,12 @@
       </c>
       <c r="G413" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr">
         <is>
-          <t>8.2,8.4</t>
+          <t>7.1.1(b), 7.1.1(g), 7.1.1(h) [support: 8.2.1]</t>
         </is>
       </c>
       <c r="I413" s="5" t="inlineStr">
@@ -36553,12 +36601,12 @@
       </c>
       <c r="G414" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr">
         <is>
-          <t>8.3,8.4,8.7</t>
+          <t>7.1.1(b), 7.1.1(g), 7.1.1(i), 7.1.4 [support: 8.2.1]</t>
         </is>
       </c>
       <c r="I414" s="5" t="inlineStr">
@@ -36622,12 +36670,12 @@
       </c>
       <c r="G415" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr">
         <is>
-          <t>8.2,8.4</t>
+          <t>7.1.1(d), 7.1.1(g) [support: 8.2.1]</t>
         </is>
       </c>
       <c r="I415" s="5" t="inlineStr">
@@ -36691,12 +36739,12 @@
       </c>
       <c r="G416" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr">
         <is>
-          <t>8.2,8.3</t>
+          <t>7.1.1(c), 7.1.1(d), 7.1.1(e)</t>
         </is>
       </c>
       <c r="I416" s="5" t="inlineStr">
@@ -36760,12 +36808,12 @@
       </c>
       <c r="G417" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr">
         <is>
-          <t>8.3,8.4,8.6</t>
+          <t>7.1.1(b), 7.1.1(f), 7.1.1(h)</t>
         </is>
       </c>
       <c r="I417" s="5" t="inlineStr">
@@ -36829,12 +36877,12 @@
       </c>
       <c r="G418" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr">
         <is>
-          <t>8.2,8.3,8.4</t>
+          <t>7.1.1(b), 7.1.1(g), 7.1.1(h)</t>
         </is>
       </c>
       <c r="I418" s="5" t="inlineStr">
@@ -36898,12 +36946,12 @@
       </c>
       <c r="G419" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>7.1.1(b), 7.1.1(g), 7.1.4</t>
         </is>
       </c>
       <c r="I419" s="5" t="inlineStr">
@@ -36967,12 +37015,12 @@
       </c>
       <c r="G420" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr">
         <is>
-          <t>8.4,8.6,8.7</t>
+          <t>7.1.1(b), 7.1.1(h), 7.1.1(i), 7.1.4</t>
         </is>
       </c>
       <c r="I420" s="5" t="inlineStr">
@@ -37036,12 +37084,12 @@
       </c>
       <c r="G421" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr">
         <is>
-          <t>8.4,8.6</t>
+          <t>7.1.1(g), 7.1.1(h)</t>
         </is>
       </c>
       <c r="I421" s="5" t="inlineStr">
@@ -37105,12 +37153,12 @@
       </c>
       <c r="G422" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr">
         <is>
-          <t>8.1,9.5</t>
+          <t>7.1.1(i), 7.1.4</t>
         </is>
       </c>
       <c r="I422" s="5" t="inlineStr">
@@ -37174,12 +37222,12 @@
       </c>
       <c r="G423" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr">
         <is>
-          <t>8.3,8.4</t>
+          <t>7.1.1(d), 7.1.1(g) [support: 8.2.1]</t>
         </is>
       </c>
       <c r="I423" s="5" t="inlineStr">
@@ -37243,12 +37291,12 @@
       </c>
       <c r="G424" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr">
         <is>
-          <t>8.1,9.5</t>
+          <t>7.1.1(i), 7.1.4</t>
         </is>
       </c>
       <c r="I424" s="5" t="inlineStr">
@@ -37312,12 +37360,12 @@
       </c>
       <c r="G425" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr">
         <is>
-          <t>8.4,8.6</t>
+          <t>7.1.1(d), 7.1.1(g) [support: 8.2.1]</t>
         </is>
       </c>
       <c r="I425" s="5" t="inlineStr">
@@ -37381,12 +37429,12 @@
       </c>
       <c r="G426" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr">
         <is>
-          <t>8.2,8.4</t>
+          <t>7.1.1(d), 7.1.1(g) [support: 8.2.1]</t>
         </is>
       </c>
       <c r="I426" s="5" t="inlineStr">
@@ -37450,12 +37498,12 @@
       </c>
       <c r="G427" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr">
         <is>
-          <t>8.3,8.6</t>
+          <t>7.1.1(g), 7.1.1(h)</t>
         </is>
       </c>
       <c r="I427" s="5" t="inlineStr">
@@ -37519,12 +37567,12 @@
       </c>
       <c r="G428" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr">
         <is>
-          <t>7.2,8.3,8.6</t>
+          <t>7.1.1(e), 7.1.1(g) [support: 7.2.2]</t>
         </is>
       </c>
       <c r="I428" s="5" t="inlineStr">
@@ -37588,12 +37636,12 @@
       </c>
       <c r="G429" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr">
         <is>
-          <t>7.3,8.3,8.6</t>
+          <t>7.1.1(g), 7.1.4</t>
         </is>
       </c>
       <c r="I429" s="5" t="inlineStr">
@@ -37657,12 +37705,12 @@
       </c>
       <c r="G430" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr">
         <is>
-          <t>8.4,8.6</t>
+          <t>7.1.1(d), 7.1.1(f)</t>
         </is>
       </c>
       <c r="I430" s="5" t="inlineStr">
@@ -37726,12 +37774,12 @@
       </c>
       <c r="G431" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr">
         <is>
-          <t>8.4,9.4</t>
+          <t>7.1.1(g) [support: 8.1.1, 8.1.2]</t>
         </is>
       </c>
       <c r="I431" s="5" t="inlineStr">
@@ -37795,12 +37843,12 @@
       </c>
       <c r="G432" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr">
         <is>
-          <t>7.2,8.3</t>
+          <t>7.1.1(g), 7.1.4 [support: 7.2.2]</t>
         </is>
       </c>
       <c r="I432" s="5" t="inlineStr">
@@ -37864,12 +37912,12 @@
       </c>
       <c r="G433" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr">
         <is>
-          <t>8.1,8.2</t>
+          <t>6.4.1, 6.4.3, 7.1.1(a), 7.1.1(d) [support: 7.3.3(a)]</t>
         </is>
       </c>
       <c r="I433" s="5" t="inlineStr">
@@ -37880,7 +37928,7 @@
       <c r="J433" s="4" t="n"/>
       <c r="K433" s="6" t="inlineStr">
         <is>
-          <t>Not immediately reportable as incident (no attack occurred). However: Section 8.1 requires incident management policy include threat intelligence consumption. Actions: enhance monitoring, review for indicators of compromise, prepare incident response team. If attack materializes: immediate classification based on impact. Pre-incident preparation is Section 8.2 (IR plan) and Section 5.1 (threat intelligence).</t>
+          <t>Not immediately reportable as incident (no attack occurred). However: Section 7.1 requires incident management to include threat-intelligence consumption (see Section 6.4). Actions: enhance monitoring, review for indicators of compromise, prepare incident response team. If attack materializes: immediate classification based on impact. Pre-incident preparation is Section 7.1 (IR plan) and Section 6.4 (threat intelligence).</t>
         </is>
       </c>
       <c r="L433" s="4" t="n"/>
@@ -37933,12 +37981,12 @@
       </c>
       <c r="G434" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.1.1(g)</t>
         </is>
       </c>
       <c r="I434" s="5" t="inlineStr">
@@ -38002,12 +38050,12 @@
       </c>
       <c r="G435" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr">
         <is>
-          <t>8.2,8.3,8.4</t>
+          <t>7.1.1(c), 7.1.1(d), 7.1.1(g) [support: 8.2.1]</t>
         </is>
       </c>
       <c r="I435" s="5" t="inlineStr">
@@ -38071,12 +38119,12 @@
       </c>
       <c r="G436" s="4" t="inlineStr">
         <is>
-          <t>CCoP 2.0 Section 8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr">
         <is>
-          <t>5.2,8.3,8.6,8.7</t>
+          <t>7.1.1(b), 7.1.1(h), 7.1.1(i), 7.1.4</t>
         </is>
       </c>
       <c r="I436" s="5" t="inlineStr">

--- a/ground-truth/expert-validation/CCoP_V2_Test_Cases_Expert_Review.xlsx
+++ b/ground-truth/expert-validation/CCoP_V2_Test_Cases_Expert_Review.xlsx
@@ -8825,7 +8825,7 @@
           <t>According to CCoP 2.0 Section 5.3.1(c), multi-factor authentication requirements are as follows:
 Required for all remote access (critical) Required for privileged accounts (critical) Required for administrative access (critical).
 The intent of this control is to ensure adequate security measures are in place for identity &amp; access management. Organizations must implement controls proportionate to their risk profile while ensuring the core requirements are met.
-Reference: CCoP 2.0, 5.2.3</t>
+Reference: CCoP 2.0 §5.3.1</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">
@@ -9701,7 +9701,7 @@
           <t>According to CCoP 2.0 Section 1.6 (Waiver), legacy system exemptions requirements are as follows:
 No blanket exemptions for legacy (critical) Compensating controls required if not compliant (critical) Must document risk and mitigation plan (important).
 The intent of this control is to ensure adequate security measures are in place for system lifecycle. Organizations must implement controls proportionate to their risk profile while ensuring the core requirements are met.
-Reference: CCoP 2.0, 4.3</t>
+Reference: CCoP 2.0 §1.6</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
@@ -9861,7 +9861,7 @@
           <t>According to CCoP 2.0 Section 3.8, supply chain control verification requirements are as follows:
 Verify software authenticity and integrity (critical) Source code escrow for critical vendors (important) Vendor security assessment required (critical).
 The intent of this control is to ensure adequate security measures are in place for supply chain security. Organizations must implement controls proportionate to their risk profile while ensuring the core requirements are met.
-Reference: CCoP 2.0, 9.3.1</t>
+Reference: CCoP 2.0 §3.8</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -9941,7 +9941,7 @@
           <t>According to CCoP 2.0 Section 5.11, mobile device management requirements are as follows:
 MDM/EMM solution required (critical) Containerization for corporate data (critical) Remote wipe capability mandatory (important).
 The intent of this control is to ensure adequate security measures are in place for endpoint security. Organizations must implement controls proportionate to their risk profile while ensuring the core requirements are met.
-Reference: CCoP 2.0, 5.3.4</t>
+Reference: CCoP 2.0 §5.11</t>
         </is>
       </c>
       <c r="L122" s="4" t="inlineStr">
@@ -10185,7 +10185,7 @@
           <t>According to CCoP 2.0 Section 5.3.1(c), mfa not required internally requirements are as follows:
 Isolated networks still require MFA (critical) Network isolation is a control, not a waiver (important) All privileged access requires MFA regardless (critical).
 The intent of this control is to ensure adequate security measures are in place for identity &amp; access management. Organizations must implement controls proportionate to their risk profile while ensuring the core requirements are met.
-Reference: CCoP 2.0, 5.2.3</t>
+Reference: CCoP 2.0 §5.3.1</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -10827,7 +10827,7 @@
 - Protects against phishing and credential theft (critical)
 - Provides layered authentication defense (important)
 Understanding control intent helps in implementing effective security measures that address the underlying threat rather than merely satisfying checkbox requirements. Organizations should consider both the letter and spirit of each control.
-Reference: CCoP 2.0, 5.2.3</t>
+Reference: CCoP 2.0 §5.3.1</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -11740,7 +11740,7 @@
 - Excessive access increases breach impact (critical)
 - Enforces least privilege over time (important)
 Understanding control intent helps in implementing effective security measures that address the underlying threat rather than merely satisfying checkbox requirements. Organizations should consider both the letter and spirit of each control.
-Reference: CCoP 2.0, 5.2.5</t>
+Reference: CCoP 2.0 §5.2.1</t>
         </is>
       </c>
       <c r="L144" s="4" t="inlineStr">
@@ -12155,7 +12155,7 @@
 - BCP provides recovery path when prevention fails (critical)
 - Addresses availability impact of incidents (important)
 Understanding control intent helps in implementing effective security measures that address the underlying threat rather than merely satisfying checkbox requirements. Organizations should consider both the letter and spirit of each control.
-Reference: CCoP 2.0, 7.4.1</t>
+Reference: CCoP 2.0 §8.2</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -12238,7 +12238,7 @@
 - Risk assessment identifies highest-priority vulnerabilities (critical)
 - Provides basis for control selection and justification (important)
 Understanding control intent helps in implementing effective security measures that address the underlying threat rather than merely satisfying checkbox requirements. Organizations should consider both the letter and spirit of each control.
-Reference: CCoP 2.0, 4.2.1</t>
+Reference: CCoP 2.0 §3.2</t>
         </is>
       </c>
       <c r="L150" s="4" t="inlineStr">
@@ -12855,7 +12855,7 @@
 2. Implement compensating controls if immediate remediation not feasible
 3. Establish ongoing monitoring to prevent recurrence
 **Risk Level:** High
-Reference: CCoP 2.0, 5.2.4</t>
+Reference: CCoP 2.0 §5.3.1</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
@@ -12944,7 +12944,7 @@
 2. Implement compensating controls if immediate remediation not feasible
 3. Establish ongoing monitoring to prevent recurrence
 **Risk Level:** High
-Reference: CCoP 2.0, 5.2.5</t>
+Reference: CCoP 2.0 §5.3.1</t>
         </is>
       </c>
       <c r="L158" s="4" t="inlineStr">
@@ -13033,7 +13033,7 @@
 2. Implement compensating controls if immediate remediation not feasible
 3. Establish ongoing monitoring to prevent recurrence
 **Risk Level:** High
-Reference: CCoP 2.0, 5.2.4</t>
+Reference: CCoP 2.0 §5.3.1</t>
         </is>
       </c>
       <c r="L159" s="4" t="inlineStr">
@@ -13207,7 +13207,7 @@
 2. Implement compensating controls if immediate remediation not feasible
 3. Establish ongoing monitoring to prevent recurrence
 **Risk Level:** High
-Reference: CCoP 2.0, 5.2.6</t>
+Reference: CCoP 2.0 §5.3.1</t>
         </is>
       </c>
       <c r="L161" s="4" t="inlineStr">
@@ -13648,7 +13648,7 @@
 2. Implement compensating controls if immediate remediation not feasible
 3. Establish ongoing monitoring to prevent recurrence
 **Risk Level:** High
-Reference: CCoP 2.0, 6.3.4</t>
+Reference: CCoP 2.0 §6.2</t>
         </is>
       </c>
       <c r="L166" s="4" t="inlineStr">
@@ -13826,7 +13826,7 @@
 2. Implement compensating controls if immediate remediation not feasible
 3. Establish ongoing monitoring to prevent recurrence
 **Risk Level:** High
-Reference: CCoP 2.0, 5.4.2</t>
+Reference: CCoP 2.0 §5.5</t>
         </is>
       </c>
       <c r="L168" s="4" t="inlineStr">
@@ -13911,7 +13911,7 @@
 2. Implement compensating controls if immediate remediation not feasible
 3. Establish ongoing monitoring to prevent recurrence
 **Risk Level:** High
-Reference: CCoP 2.0, 5.4.4</t>
+Reference: CCoP 2.0 §5.7</t>
         </is>
       </c>
       <c r="L169" s="4" t="inlineStr">
@@ -14700,7 +14700,7 @@
 2. Implement compensating controls if immediate remediation not feasible
 3. Establish ongoing monitoring to prevent recurrence
 **Risk Level:** High
-Reference: CCoP 2.0, 5.2.3</t>
+Reference: CCoP 2.0 §5.3.1</t>
         </is>
       </c>
       <c r="L178" s="4" t="inlineStr">

--- a/ground-truth/expert-validation/CCoP_V2_Test_Cases_Expert_Review.xlsx
+++ b/ground-truth/expert-validation/CCoP_V2_Test_Cases_Expert_Review.xlsx
@@ -615,7 +615,7 @@
     <row r="2" ht="225" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>B1-001</t>
+          <t>B01-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -692,7 +692,7 @@
     <row r="3" ht="225" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>B1-002</t>
+          <t>B01-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -769,7 +769,7 @@
     <row r="4" ht="210" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>B1-003</t>
+          <t>B01-003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -846,7 +846,7 @@
     <row r="5" ht="225" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>B1-004</t>
+          <t>B01-004</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -923,7 +923,7 @@
     <row r="6" ht="240" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>B1-005</t>
+          <t>B01-005</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1000,7 +1000,7 @@
     <row r="7" ht="240" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>B1-006</t>
+          <t>B01-006</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="8" ht="225" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>B1-007</t>
+          <t>B01-007</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1154,7 +1154,7 @@
     <row r="9" ht="225" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>B1-008</t>
+          <t>B01-008</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1231,7 +1231,7 @@
     <row r="10" ht="225" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>B1-009</t>
+          <t>B01-009</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1308,7 +1308,7 @@
     <row r="11" ht="255" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>B1-010</t>
+          <t>B01-010</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1385,7 +1385,7 @@
     <row r="12" ht="240" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>B1-011</t>
+          <t>B01-011</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1462,7 +1462,7 @@
     <row r="13" ht="225" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>B1-012</t>
+          <t>B01-012</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1539,7 +1539,7 @@
     <row r="14" ht="255" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>B1-013</t>
+          <t>B01-013</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="15" ht="210" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>B1-014</t>
+          <t>B01-014</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1693,7 +1693,7 @@
     <row r="16" ht="225" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>B1-015</t>
+          <t>B01-015</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1770,7 +1770,7 @@
     <row r="17" ht="225" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>B1-016</t>
+          <t>B01-016</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1847,7 +1847,7 @@
     <row r="18" ht="240" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>B1-017</t>
+          <t>B01-017</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1924,7 +1924,7 @@
     <row r="19" ht="225" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>B1-018</t>
+          <t>B01-018</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -2001,7 +2001,7 @@
     <row r="20" ht="240" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>B1-019</t>
+          <t>B01-019</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -2078,7 +2078,7 @@
     <row r="21" ht="180" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>B1-020</t>
+          <t>B01-020</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -2155,7 +2155,7 @@
     <row r="22" ht="210" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>B1-021</t>
+          <t>B01-021</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2232,7 +2232,7 @@
     <row r="23" ht="225" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>B1-022</t>
+          <t>B01-022</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -2309,7 +2309,7 @@
     <row r="24" ht="240" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>B1-023</t>
+          <t>B01-023</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -2386,7 +2386,7 @@
     <row r="25" ht="240" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>B1-024</t>
+          <t>B01-024</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="26" ht="255" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>B1-025</t>
+          <t>B01-025</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -2540,7 +2540,7 @@
     <row r="27" ht="180" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>B2-001</t>
+          <t>B02-001</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -2617,7 +2617,7 @@
     <row r="28" ht="180" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>B2-002</t>
+          <t>B02-002</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -2694,7 +2694,7 @@
     <row r="29" ht="165" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>B2-003</t>
+          <t>B02-003</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -2771,7 +2771,7 @@
     <row r="30" ht="195" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>B2-004</t>
+          <t>B02-004</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -2848,7 +2848,7 @@
     <row r="31" ht="195" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>B2-005</t>
+          <t>B02-005</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -2925,7 +2925,7 @@
     <row r="32" ht="150" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>B2-006</t>
+          <t>B02-006</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -3002,7 +3002,7 @@
     <row r="33" ht="165" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>B2-007</t>
+          <t>B02-007</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="34" ht="165" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>B2-008</t>
+          <t>B02-008</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -3156,7 +3156,7 @@
     <row r="35" ht="195" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>B2-009</t>
+          <t>B02-009</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -3233,7 +3233,7 @@
     <row r="36" ht="180" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>B2-010</t>
+          <t>B02-010</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -3310,7 +3310,7 @@
     <row r="37" ht="210" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>B2-011</t>
+          <t>B02-011</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -3387,7 +3387,7 @@
     <row r="38" ht="210" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>B2-012</t>
+          <t>B02-012</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -3464,7 +3464,7 @@
     <row r="39" ht="180" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>B2-013</t>
+          <t>B02-013</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -3541,7 +3541,7 @@
     <row r="40" ht="240" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>B2-014</t>
+          <t>B02-014</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -3618,7 +3618,7 @@
     <row r="41" ht="225" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>B2-015</t>
+          <t>B02-015</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -3695,7 +3695,7 @@
     <row r="42" ht="225" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>B2-016</t>
+          <t>B02-016</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -3772,7 +3772,7 @@
     <row r="43" ht="180" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>B2-017</t>
+          <t>B02-017</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -3849,7 +3849,7 @@
     <row r="44" ht="195" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>B2-018</t>
+          <t>B02-018</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -3926,7 +3926,7 @@
     <row r="45" ht="225" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>B2-019</t>
+          <t>B02-019</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -4003,7 +4003,7 @@
     <row r="46" ht="225" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>B2-020</t>
+          <t>B02-020</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -4080,7 +4080,7 @@
     <row r="47" ht="225" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>B2-021</t>
+          <t>B02-021</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -4157,7 +4157,7 @@
     <row r="48" ht="195" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>B2-022</t>
+          <t>B02-022</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -4234,7 +4234,7 @@
     <row r="49" ht="210" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>B2-023</t>
+          <t>B02-023</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -4311,7 +4311,7 @@
     <row r="50" ht="240" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>B2-024</t>
+          <t>B02-024</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -4388,7 +4388,7 @@
     <row r="51" ht="240" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>B2-025</t>
+          <t>B02-025</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -4465,7 +4465,7 @@
     <row r="52" ht="150" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>B3-001</t>
+          <t>B03-001</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -4542,7 +4542,7 @@
     <row r="53" ht="150" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>B3-002</t>
+          <t>B03-002</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -4619,7 +4619,7 @@
     <row r="54" ht="60" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>B3-003</t>
+          <t>B03-003</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -4696,7 +4696,7 @@
     <row r="55" ht="75" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>B3-004</t>
+          <t>B03-004</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -4773,7 +4773,7 @@
     <row r="56" ht="75" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>B3-005</t>
+          <t>B03-005</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -4850,7 +4850,7 @@
     <row r="57" ht="75" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>B3-006</t>
+          <t>B03-006</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="58" ht="75" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>B3-007</t>
+          <t>B03-007</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -5004,7 +5004,7 @@
     <row r="59" ht="75" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>B3-008</t>
+          <t>B03-008</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -5081,7 +5081,7 @@
     <row r="60" ht="75" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>B3-009</t>
+          <t>B03-009</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -5158,7 +5158,7 @@
     <row r="61" ht="60" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>B3-010</t>
+          <t>B03-010</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -5235,7 +5235,7 @@
     <row r="62" ht="75" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>B3-011</t>
+          <t>B03-011</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -5312,7 +5312,7 @@
     <row r="63" ht="75" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>B3-012</t>
+          <t>B03-012</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -5389,7 +5389,7 @@
     <row r="64" ht="90" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>B3-013</t>
+          <t>B03-013</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -5466,7 +5466,7 @@
     <row r="65" ht="75" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>B3-014</t>
+          <t>B03-014</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -5543,7 +5543,7 @@
     <row r="66" ht="75" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>B3-015</t>
+          <t>B03-015</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -5620,7 +5620,7 @@
     <row r="67" ht="60" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>B3-016</t>
+          <t>B03-016</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -5697,7 +5697,7 @@
     <row r="68" ht="75" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>B3-017</t>
+          <t>B03-017</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -5774,7 +5774,7 @@
     <row r="69" ht="75" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>B3-018</t>
+          <t>B03-018</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -5851,7 +5851,7 @@
     <row r="70" ht="75" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>B3-019</t>
+          <t>B03-019</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -5928,7 +5928,7 @@
     <row r="71" ht="75" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>B3-020</t>
+          <t>B03-020</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -6005,7 +6005,7 @@
     <row r="72" ht="75" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>B3-021</t>
+          <t>B03-021</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -6082,7 +6082,7 @@
     <row r="73" ht="75" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>B3-022</t>
+          <t>B03-022</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -6159,7 +6159,7 @@
     <row r="74" ht="75" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>B3-023</t>
+          <t>B03-023</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -6236,7 +6236,7 @@
     <row r="75" ht="75" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>B3-024</t>
+          <t>B03-024</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -6313,7 +6313,7 @@
     <row r="76" ht="75" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>B3-025</t>
+          <t>B03-025</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -6390,7 +6390,7 @@
     <row r="77" ht="75" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>B3-026</t>
+          <t>B03-026</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -6467,7 +6467,7 @@
     <row r="78" ht="60" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>B3-027</t>
+          <t>B03-027</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -6544,7 +6544,7 @@
     <row r="79" ht="60" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>B3-028</t>
+          <t>B03-028</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -6621,7 +6621,7 @@
     <row r="80" ht="75" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>B3-029</t>
+          <t>B03-029</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -6694,7 +6694,7 @@
     <row r="81" ht="75" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>B3-030</t>
+          <t>B03-030</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
